--- a/Отчет_ОАО.xlsx
+++ b/Отчет_ОАО.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>к-во</t>
+          <t>к-во/р.с</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C43" s="17" t="n">
-        <v>3274642.24</v>
+        <v>3274642</v>
       </c>
       <c r="D43" s="17" t="n">
         <v>0</v>
       </c>
       <c r="E43" s="36" t="n">
-        <v>3274642.24</v>
+        <v>3274642</v>
       </c>
     </row>
     <row r="44">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="C44" s="17" t="n">
-        <v>1711211.74</v>
+        <v>1711212.95</v>
       </c>
       <c r="D44" s="17" t="n">
         <v>0</v>
       </c>
       <c r="E44" s="36" t="n">
-        <v>1711211.74</v>
+        <v>1711212.95</v>
       </c>
     </row>
     <row r="45">
@@ -1539,13 +1539,13 @@
         </is>
       </c>
       <c r="C45" s="17" t="n">
-        <v>131662.11</v>
+        <v>131662</v>
       </c>
       <c r="D45" s="17" t="n">
         <v>0</v>
       </c>
       <c r="E45" s="36" t="n">
-        <v>131662.11</v>
+        <v>131662</v>
       </c>
     </row>
     <row r="46" ht="25.5" customHeight="1">
